--- a/artfynd/A 16910-2025 artfynd.xlsx
+++ b/artfynd/A 16910-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436330</v>
       </c>
       <c r="B2" t="n">
-        <v>98589</v>
+        <v>98596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>127436351</v>
       </c>
       <c r="B3" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127436331</v>
       </c>
       <c r="B4" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>127436347</v>
       </c>
       <c r="B5" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16910-2025 artfynd.xlsx
+++ b/artfynd/A 16910-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436330</v>
       </c>
       <c r="B2" t="n">
-        <v>98596</v>
+        <v>98598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>127436351</v>
       </c>
       <c r="B3" t="n">
-        <v>96922</v>
+        <v>96924</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127436331</v>
       </c>
       <c r="B4" t="n">
-        <v>96922</v>
+        <v>96924</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>127436347</v>
       </c>
       <c r="B5" t="n">
-        <v>96922</v>
+        <v>96924</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16910-2025 artfynd.xlsx
+++ b/artfynd/A 16910-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436330</v>
       </c>
       <c r="B2" t="n">
-        <v>98598</v>
+        <v>98624</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>127436351</v>
       </c>
       <c r="B3" t="n">
-        <v>96924</v>
+        <v>96950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127436331</v>
       </c>
       <c r="B4" t="n">
-        <v>96924</v>
+        <v>96950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>127436347</v>
       </c>
       <c r="B5" t="n">
-        <v>96924</v>
+        <v>96950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16910-2025 artfynd.xlsx
+++ b/artfynd/A 16910-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436330</v>
       </c>
       <c r="B2" t="n">
-        <v>98624</v>
+        <v>98625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>127436351</v>
       </c>
       <c r="B3" t="n">
-        <v>96950</v>
+        <v>96951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127436331</v>
       </c>
       <c r="B4" t="n">
-        <v>96950</v>
+        <v>96951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>127436347</v>
       </c>
       <c r="B5" t="n">
-        <v>96950</v>
+        <v>96951</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16910-2025 artfynd.xlsx
+++ b/artfynd/A 16910-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436330</v>
       </c>
       <c r="B2" t="n">
-        <v>98625</v>
+        <v>98626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>127436351</v>
       </c>
       <c r="B3" t="n">
-        <v>96951</v>
+        <v>96952</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127436331</v>
       </c>
       <c r="B4" t="n">
-        <v>96951</v>
+        <v>96952</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>127436347</v>
       </c>
       <c r="B5" t="n">
-        <v>96951</v>
+        <v>96952</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16910-2025 artfynd.xlsx
+++ b/artfynd/A 16910-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436330</v>
       </c>
       <c r="B2" t="n">
-        <v>98626</v>
+        <v>98630</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>127436351</v>
       </c>
       <c r="B3" t="n">
-        <v>96952</v>
+        <v>96956</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>127436331</v>
       </c>
       <c r="B4" t="n">
-        <v>96952</v>
+        <v>96956</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>127436347</v>
       </c>
       <c r="B5" t="n">
-        <v>96952</v>
+        <v>96956</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16910-2025 artfynd.xlsx
+++ b/artfynd/A 16910-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436330</v>
       </c>
       <c r="B2" t="n">
-        <v>98676</v>
+        <v>98688</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127436351</v>
       </c>
       <c r="B3" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>127436331</v>
       </c>
       <c r="B4" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>127436347</v>
       </c>
       <c r="B5" t="n">
-        <v>97002</v>
+        <v>97014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16910-2025 artfynd.xlsx
+++ b/artfynd/A 16910-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436330</v>
       </c>
       <c r="B2" t="n">
-        <v>98688</v>
+        <v>98689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127436351</v>
       </c>
       <c r="B3" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>127436331</v>
       </c>
       <c r="B4" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>127436347</v>
       </c>
       <c r="B5" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16910-2025 artfynd.xlsx
+++ b/artfynd/A 16910-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436330</v>
       </c>
       <c r="B2" t="n">
-        <v>98689</v>
+        <v>98694</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127436351</v>
       </c>
       <c r="B3" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>127436331</v>
       </c>
       <c r="B4" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>127436347</v>
       </c>
       <c r="B5" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16910-2025 artfynd.xlsx
+++ b/artfynd/A 16910-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436330</v>
       </c>
       <c r="B2" t="n">
-        <v>98694</v>
+        <v>98698</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127436351</v>
       </c>
       <c r="B3" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>127436331</v>
       </c>
       <c r="B4" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>127436347</v>
       </c>
       <c r="B5" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16910-2025 artfynd.xlsx
+++ b/artfynd/A 16910-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436330</v>
       </c>
       <c r="B2" t="n">
-        <v>98698</v>
+        <v>98700</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127436351</v>
       </c>
       <c r="B3" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>127436331</v>
       </c>
       <c r="B4" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>127436347</v>
       </c>
       <c r="B5" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16910-2025 artfynd.xlsx
+++ b/artfynd/A 16910-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127436330</v>
       </c>
       <c r="B2" t="n">
-        <v>98700</v>
+        <v>98710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>127436351</v>
       </c>
       <c r="B3" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>127436331</v>
       </c>
       <c r="B4" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>127436347</v>
       </c>
       <c r="B5" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16910-2025 artfynd.xlsx
+++ b/artfynd/A 16910-2025 artfynd.xlsx
@@ -675,30 +675,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127436330</v>
+        <v>127436331</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527647</v>
+        <v>527661</v>
       </c>
       <c r="R2" t="n">
-        <v>6639490</v>
+        <v>6639532</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127436351</v>
+        <v>127436347</v>
       </c>
       <c r="B3" t="n">
-        <v>97036</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>527724</v>
+        <v>527614</v>
       </c>
       <c r="R3" t="n">
-        <v>6639661</v>
+        <v>6639653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,21 +866,6 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>Äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Tallåga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -898,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127436331</v>
+        <v>127436351</v>
       </c>
       <c r="B4" t="n">
-        <v>97036</v>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>527661</v>
+        <v>527724</v>
       </c>
       <c r="R4" t="n">
-        <v>6639532</v>
+        <v>6639661</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,6 +972,21 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>Äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Tallåga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1004,34 +1008,30 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127436347</v>
+        <v>127436330</v>
       </c>
       <c r="B5" t="n">
-        <v>97036</v>
+        <v>99038</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>223597</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>527614</v>
+        <v>527647</v>
       </c>
       <c r="R5" t="n">
-        <v>6639653</v>
+        <v>6639490</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
